--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-frameworks-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-frameworks-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Sơ đồ Venn giúp BA trực quan hóa các tính năng trùng nhau giữa hệ thống cũ và mới, từ đó xác định rõ phạm vi (scope) chuyển đổi dữ liệu và phát triển tính năng mới.</v>
       </c>
       <c r="F2" t="str">
+        <v>Tổng chi phí bản quyền phần mềm phải trả cho hai nhà cung cấp khác nhau — so sánh chi phí</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Độ tuổi trung bình của tập người dùng sử dụng hai hệ thống này — so sánh nhân khẩu học</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Tốc độ tải dữ liệu trung bình giữa hai hệ thống trên cùng một cấu hình phần cứng — so sánh hiệu năng</v>
+      </c>
+      <c r="I2" t="str">
         <v>Sự giao thoa về tính năng để xác định phần nào cần giữ lại, phần nào cần loại bỏ và phần nào cần xây mới — so sánh tập hợp tính năng</v>
       </c>
-      <c r="G2" t="str">
-        <v>Tốc độ tải dữ liệu trung bình giữa hai hệ thống trên cùng một cấu hình phần cứng — so sánh hiệu năng</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Tổng chi phí bản quyền phần mềm phải trả cho hai nhà cung cấp khác nhau — so sánh chi phí</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Độ tuổi trung bình của tập người dùng sử dụng hai hệ thống này — so sánh nhân khẩu học</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Mô hình Kano giúp đánh giá mức độ hài lòng của khách hàng đối với các tính năng. Tính năng "Must-be" là bắt buộc phải có; "Attractive" là tính năng gây bất ngờ, tạo lợi thế cạnh tranh.</v>
       </c>
       <c r="F3" t="str">
+        <v>Immediate, Short-term, Long-term, Future — phân loại tiến độ bàn giao</v>
+      </c>
+      <c r="G3" t="str">
         <v>Must-be (Cơ bản), One-dimensional (Hiệu năng), Attractive (Hấp dẫn), Indifferent (Thờ ơ), Reverse (Ngược chiều) — phân loại trải nghiệm người dùng</v>
-      </c>
-      <c r="G3" t="str">
-        <v>High, Medium, Low, Critical — phân loại mức độ nghiêm trọng của lỗi phần mềm</v>
       </c>
       <c r="H3" t="str">
         <v>Functional, Non-functional, Technical, Business — phân loại thuộc tính yêu cầu</v>
       </c>
       <c r="I3" t="str">
-        <v>Immediate, Short-term, Long-term, Future — phân loại tiến độ bàn giao</v>
+        <v>High, Medium, Low, Critical — phân loại mức độ nghiêm trọng của lỗi phần mềm</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Ma trận Power-Interest chia stakeholders thành 4 nhóm: Quyền lực cao/Quan tâm cao (Key Players - cần quản lý chặt chẽ), Quyền lực cao/Quan tâm thấp (Keep Satisfied), Quyền lực thấp/Quan tâm cao (Keep Informed), Quyền lực thấp/Quan tâm thấp (Monitor).</v>
       </c>
       <c r="F4" t="str">
-        <v>Mức độ ảnh hưởng (Power/Influence) và Mức độ quan tâm (Interest) đối với dự án — ma trận Power-Interest</v>
+        <v>Độ tuổi trung bình (Age) và Vị trí địa lý nơi họ sinh sống (Location) — ma trận nhân khẩu học</v>
       </c>
       <c r="G4" t="str">
         <v>Năng lực kỹ thuật lập trình (Technical skill) và Số năm kinh nghiệm làm việc (Experience) — ma trận năng lực</v>
       </c>
       <c r="H4" t="str">
+        <v>Mức độ ảnh hưởng (Power/Influence) và Mức độ quan tâm (Interest) đối với dự án — ma trận Power-Interest</v>
+      </c>
+      <c r="I4" t="str">
         <v>Mức lương hàng tháng (Salary) và Số giờ làm việc cam kết trong dự án (Working hours) — ma trận chi phí</v>
       </c>
-      <c r="I4" t="str">
-        <v>Độ tuổi trung bình (Age) và Vị trí địa lý nơi họ sinh sống (Location) — ma trận nhân khẩu học</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Biểu đồ xương cá phân nhóm nguyên nhân thành các loại (Con người, Quy trình, Máy móc...). Tại mỗi nhánh nguyên nhân, BA áp dụng câu hỏi 5 Why để đào sâu tìm nguyên nhân gốc rễ.</v>
       </c>
       <c r="F5" t="str">
+        <v>Phương pháp tính toán điểm ưu tiên RICE của Product Backlog — sắp xếp độ ưu tiên</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Quy trình viết kịch bản kiểm thử tự động Given-When-Then — thiết kế test case</v>
+      </c>
+      <c r="H5" t="str">
         <v>Phương pháp đặt câu hỏi 5 Why liên tiếp ở từng nhánh xương cá — tìm nguyên nhân gốc rễ đa chiều</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Kỹ thuật ước lượng Story Point bằng Planning Poker trong sprint — ước lượng độ phức tạp</v>
       </c>
-      <c r="H5" t="str">
-        <v>Phương pháp tính toán điểm ưu tiên RICE của Product Backlog — sắp xếp độ ưu tiên</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Quy trình viết kịch bản kiểm thử tự động Given-When-Then — thiết kế test case</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Value Proposition Canvas (VPC) đi sâu vào chi tiết của 2 ô này, giúp BA thiết kế sản phẩm khớp (fit) giữa Pain Relievers/Gain Creators của sản phẩm với Pains/Gains của phân khúc khách hàng.</v>
       </c>
       <c r="F6" t="str">
+        <v>Sơ đồ phân rã chức năng hệ thống (Functional Decomposition) — sơ đồ chức năng</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Biểu đồ luồng dữ liệu cấp 0 (Data Flow Diagram Level 0) — sơ đồ luồng dữ liệu</v>
+      </c>
+      <c r="H6" t="str">
         <v>Value Proposition Canvas (VPC) với sơ đồ Khớp (Fit) giữa Customer Profile và Value Map — bản đồ tuyên bố giá trị</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Sơ đồ phân rã chức năng hệ thống (Functional Decomposition) — sơ đồ chức năng</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Biểu đồ luồng dữ liệu cấp 0 (Data Flow Diagram Level 0) — sơ đồ luồng dữ liệu</v>
       </c>
       <c r="I6" t="str">
         <v>Mô hình phân tích chuỗi giá trị của Michael Porter (Value Chain) — sơ đồ chuỗi giá trị</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Chiến lược S-O sử dụng những điểm mạnh bên trong để khai thác triệt để các cơ hội mở ra từ môi trường bên ngoài, tạo bước đột phá kinh doanh.</v>
       </c>
       <c r="F7" t="str">
+        <v>Bỏ qua hoàn toàn các điểm yếu nội bộ để tập trung mua lại các công ty đối thủ — thâu tóm thị trường</v>
+      </c>
+      <c r="G7" t="str">
         <v>Sử dụng chiến lược kết hợp S-O (Strengths - Opportunities) để phát huy tối đa lợi thế cạnh tranh — chiến lược tấn công</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Sử dụng chiến lược kết hợp W-T (Weaknesses - Threats) để giảm thiểu rủi ro đóng cửa công ty — chiến lược phòng thủ</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Bỏ qua hoàn toàn các điểm yếu nội bộ để tập trung mua lại các công ty đối thủ — thâu tóm thị trường</v>
       </c>
       <c r="I7" t="str">
         <v>Yêu cầu đội ngũ lập trình viên tự bỏ tiền túi ra mua thêm máy chủ Cloud mới — cắt giảm chi phí</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -655,13 +655,13 @@
         <v>Duy trì tính truy vết yêu cầu (Traceability), phê duyệt thay đổi (Change control) và sắp xếp độ ưu tiên yêu cầu — quản trị yêu cầu</v>
       </c>
       <c r="G8" t="str">
+        <v>Chạy thử nghiệm phần mềm thực tế với người dùng cuối ở giai đoạn UAT — kiểm thử nghiệm thu</v>
+      </c>
+      <c r="H8" t="str">
         <v>Tuyển dụng nhân sự và đào tạo kỹ năng lập trình cho các developer mới — quản lý nhân sự</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>Viết mã nguồn bằng ngôn ngữ TypeScript và triển khai lên môi trường AWS — triển khai kỹ thuật</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Chạy thử nghiệm phần mềm thực tế với người dùng cuối ở giai đoạn UAT — kiểm thử nghiệm thu</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -684,19 +684,19 @@
         <v>Các nghị định, luật lệ mới ban hành từ chính phủ là các ràng buộc vĩ mô thuộc nhóm Legal (Pháp lý) hoặc Political (Chính trị) trong mô hình PESTEL.</v>
       </c>
       <c r="F9" t="str">
-        <v>Legal (Pháp lý) hoặc Political (Chính trị) — các quy định pháp luật và chính sách quản lý</v>
+        <v>Technological (Công nghệ) hoặc Economic (Kinh tế) — hạ tầng kỹ thuật và lạm phát tiền tệ</v>
       </c>
       <c r="G9" t="str">
         <v>Environmental (Môi trường) hoặc Social (Xã hội) — các yếu tố tự nhiên và xu hướng văn hóa</v>
       </c>
       <c r="H9" t="str">
-        <v>Technological (Công nghệ) hoặc Economic (Kinh tế) — hạ tầng kỹ thuật và lạm phát tiền tệ</v>
+        <v>Legal (Pháp lý) hoặc Political (Chính trị) — các quy định pháp luật và chính sách quản lý</v>
       </c>
       <c r="I9" t="str">
         <v>Nội tại điểm yếu (Weakness) của phần mềm ví điện tử đang phát triển — yếu tố nội bộ</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Phân tích Cost-Benefit (Chi phí - Lợi ích) kết hợp ma trận ưu tiên yêu cầu theo mục tiêu chiến lược của doanh nghiệp — phân tích kinh tế định lượng</v>
       </c>
       <c r="G10" t="str">
+        <v>Chạy kịch bản test hiệu năng hệ thống bằng công cụ Apache JMeter — kiểm thử kỹ thuật</v>
+      </c>
+      <c r="H10" t="str">
         <v>Sơ đồ phân rã Use Case UML của hệ thống tổng đài tự động — phân tích ca sử dụng</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>Ma trận RACI để xác định xem ai là người có lương cao hơn để nghe theo ý kiến họ — dựa trên cấp bậc</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Chạy kịch bản test hiệu năng hệ thống bằng công cụ Apache JMeter — kiểm thử kỹ thuật</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -748,19 +748,19 @@
         <v>Gap Analysis giúp làm rõ những gì hệ thống hiện tại chưa làm được so với mục tiêu đặt ra, từ đó định hình phạm vi công việc cần thực hiện trong dự án.</v>
       </c>
       <c r="F11" t="str">
-        <v>Xác định khoảng cách giữa trạng thái hiện tại (Current State) và trạng thái tương lai mong muốn (Future State) để lên kế hoạch hành động — xác định khoảng trống nghiệp vụ</v>
+        <v>Đo lường thời gian trễ của đường truyền internet giữa văn phòng khách hàng và máy chủ dự án — đo lường mạng</v>
       </c>
       <c r="G11" t="str">
-        <v>Đo lường thời gian trễ của đường truyền internet giữa văn phòng khách hàng và máy chủ dự án — đo lường mạng</v>
+        <v>So sánh các giao diện phần mềm của 3 đối thủ cạnh tranh lớn nhất trên thị trường — phân tích đối thủ</v>
       </c>
       <c r="H11" t="str">
         <v>Tìm kiếm các lập trình viên đang rảnh việc trong công ty để phân bổ vào dự án mới — quản lý tài nguyên</v>
       </c>
       <c r="I11" t="str">
-        <v>So sánh các giao diện phần mềm của 3 đối thủ cạnh tranh lớn nhất trên thị trường — phân tích đối thủ</v>
+        <v>Xác định khoảng cách giữa trạng thái hiện tại (Current State) và trạng thái tương lai mong muốn (Future State) để lên kế hoạch hành động — xác định khoảng trống nghiệp vụ</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
